--- a/isolated_excel/Newey-West Inference.xlsx
+++ b/isolated_excel/Newey-West Inference.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Newey-West'!$A$1:$F$4</definedName>

--- a/isolated_excel/Newey-West Inference.xlsx
+++ b/isolated_excel/Newey-West Inference.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Newey-West'!$A$1:$F$4</definedName>
@@ -443,9 +443,9 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,19 +487,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3772386842921072</v>
+        <v>0.3747761591438624</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.265277884999726</v>
+        <v>9.393911403356611</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.5317281488808968</v>
+        <v>0.5288328374812032</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.573323692368519</v>
+        <v>6.657328716303208</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.525269540287813</v>
+        <v>3.553834897000299</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3947853253499741</v>
+        <v>0.3917940053800512</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.929586065952908</v>
+        <v>9.070671955669612</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5895925187557978</v>
+        <v>0.5847909478065225</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>5.979162604924332</v>
+        <v>6.077103126049211</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02263441138176098</v>
+        <v>-0.02540694158567561</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.0837408984724622</v>
+        <v>0.08345823680342875</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.2702910023016316</v>
+        <v>-0.3044270111471107</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1067711854776375</v>
+        <v>0.1060104541983708</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2119898854780591</v>
+        <v>-0.2396644913730222</v>
       </c>
     </row>
   </sheetData>
@@ -597,7 +597,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Newey-West Inference.xlsx
+++ b/isolated_excel/Newey-West Inference.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Newey-West'!$A$1:$F$4</definedName>
@@ -443,7 +443,7 @@
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -487,19 +487,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3747761591438624</v>
+        <v>0.3715046783874216</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.393911403356611</v>
+        <v>9.473577226931436</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.5288328374812032</v>
+        <v>0.5241488622315456</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.657328716303208</v>
+        <v>6.714654012384019</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.553834897000299</v>
+        <v>3.552270603645034</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3917940053800512</v>
+        <v>0.3882041321353366</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.070671955669612</v>
+        <v>9.150522391674681</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5847909478065225</v>
+        <v>0.5791256161049188</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.077103126049211</v>
+        <v>6.133851628834663</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02540694158567561</v>
+        <v>-0.02530998899887835</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.08345823680342875</v>
+        <v>0.08305537019862617</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.3044270111471107</v>
+        <v>-0.3047363335850498</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1060104541983708</v>
+        <v>0.1058495973296159</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2396644913730222</v>
+        <v>-0.2391127565659318</v>
       </c>
     </row>
   </sheetData>
@@ -597,7 +597,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Newey-West Inference.xlsx
+++ b/isolated_excel/Newey-West Inference.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Newey-West" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Newey-West'!$A$1:$F$4</definedName>
@@ -487,19 +487,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.3715046783874216</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.473577226931436</v>
+        <v>9.473577226931443</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0.5241488622315456</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.714654012384019</v>
+        <v>6.714654012384022</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.552270603645034</v>
+        <v>3.552270603645037</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.3882041321353366</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.150522391674681</v>
+        <v>9.150522391674688</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5791256161049188</v>
+        <v>0.5791256161049186</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.133851628834663</v>
+        <v>6.133851628834669</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02530998899887835</v>
+        <v>-0.02530998899887851</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.08305537019862617</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.3047363335850498</v>
+        <v>-0.3047363335850518</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1058495973296159</v>
+        <v>0.1058495973296158</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2391127565659318</v>
+        <v>-0.2391127565659335</v>
       </c>
     </row>
   </sheetData>
